--- a/source/_static/report/PRP1_sample_r51.xlsx
+++ b/source/_static/report/PRP1_sample_r51.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\office\counter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\siq\github\cop5\source\_static\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6673A05A-FAA2-47EB-819D-FC13717F4371}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4B1344-FB84-4CF0-AB71-B7E585175E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRP1_sample_r51" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>Institution_ID</t>
   </si>
   <si>
-    <t>ISNI:1234123412341234</t>
-  </si>
-  <si>
     <t>Metric_Types</t>
   </si>
   <si>
@@ -235,6 +232,9 @@
   </si>
   <si>
     <t>Unspecified</t>
+  </si>
+  <si>
+    <t>P1:1234; ISNI:1234123412341234</t>
   </si>
 </sst>
 </file>
@@ -273,12 +273,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -404,7 +404,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -460,126 +460,126 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="D16" s="2">
         <v>10445</v>
@@ -623,13 +623,13 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="2">
         <v>7837</v>
@@ -673,13 +673,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="2">
         <v>9986</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2">
         <v>7491</v>
@@ -773,13 +773,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="2">
         <v>9825</v>
@@ -823,13 +823,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="2">
         <v>7369</v>
@@ -873,13 +873,13 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D22" s="2">
         <v>6141</v>
@@ -923,13 +923,13 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" s="2">
         <v>10625</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="2">
         <v>7972</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="2">
         <v>10577</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2">
         <v>7934</v>
@@ -1123,13 +1123,13 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" s="2">
         <v>10569</v>
@@ -1173,13 +1173,13 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" s="2">
         <v>7929</v>
@@ -1223,13 +1223,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D29" s="2">
         <v>10189</v>
@@ -1273,13 +1273,13 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D30" s="2">
         <v>7642</v>
@@ -1323,13 +1323,13 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D31" s="2">
         <v>10628</v>
@@ -1373,13 +1373,13 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2">
         <v>7974</v>
@@ -1423,13 +1423,13 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33" s="2">
         <v>10599</v>
@@ -1473,13 +1473,13 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2">
         <v>7949</v>
@@ -1523,13 +1523,13 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="2">
         <v>11653</v>
@@ -1573,13 +1573,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36" s="2">
         <v>8742</v>
@@ -1623,13 +1623,13 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37" s="2">
         <v>10111</v>
@@ -1673,13 +1673,13 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2">
         <v>7585</v>
@@ -1723,13 +1723,13 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D39" s="2">
         <v>11727</v>
@@ -1773,13 +1773,13 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="2">
         <v>8796</v>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41" s="2">
         <v>10060</v>
@@ -1873,13 +1873,13 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="2">
         <v>7545</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D43" s="2">
         <v>10437</v>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D44" s="2">
         <v>7829</v>
@@ -2023,13 +2023,13 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D45" s="2">
         <v>10752</v>
@@ -2073,13 +2073,13 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D46" s="2">
         <v>8066</v>
@@ -2123,13 +2123,13 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D47" s="2">
         <v>10774</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D48" s="2">
         <v>8081</v>
@@ -2223,13 +2223,13 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D49" s="2">
         <v>196697</v>
@@ -2273,13 +2273,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D50" s="2">
         <v>9729</v>
@@ -2323,13 +2323,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D51" s="2">
         <v>7298</v>
@@ -2373,13 +2373,13 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D52" s="2">
         <v>9314</v>
@@ -2423,13 +2423,13 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D53" s="2">
         <v>7098</v>
@@ -2473,13 +2473,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D54" s="2">
         <v>2757</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D55" s="2">
         <v>11553</v>
@@ -2573,13 +2573,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D56" s="2">
         <v>8666</v>
@@ -2623,13 +2623,13 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D57" s="2">
         <v>10829</v>
@@ -2673,13 +2673,13 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D58" s="2">
         <v>8123</v>
@@ -2723,13 +2723,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D59" s="2">
         <v>11072</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D60" s="2">
         <v>8304</v>
@@ -2823,13 +2823,13 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D61" s="2">
         <v>10670</v>
@@ -2873,13 +2873,13 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D62" s="2">
         <v>8003</v>
@@ -2923,13 +2923,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D63" s="2">
         <v>11888</v>
@@ -2973,13 +2973,13 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D64" s="2">
         <v>8919</v>
@@ -3023,13 +3023,13 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D65" s="2">
         <v>10730</v>
@@ -3073,13 +3073,13 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D66" s="2">
         <v>8050</v>
